--- a/docs/design/2026-09-10-hunt-stage-design/GameXXK_讨伐与宝箱设计总表_2026-09-10.xlsx
+++ b/docs/design/2026-09-10-hunt-stage-design/GameXXK_讨伐与宝箱设计总表_2026-09-10.xlsx
@@ -801,7 +801,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仅作用于装备/宝石品质；高于稀有的每档概率精确4倍。原类别概率和门票的额外/替代口径另行记录。</t>
+          <t>装备/宝石分支的条件品质概率；各高品质档精确4倍。先判定门票替代，因此不是每个箱子的无条件出货概率。</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>已确定项和未答项独立记录，不把一个问题的批准扩大到其他未回答的设计决定。</t>
+          <t>来源难度与替代奖励均已得到用户确认；实现和验证状态另列。</t>
         </is>
       </c>
     </row>
@@ -1077,17 +1077,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Question pending: source difficulty versus random distribution</t>
+          <t>按取得时保存的箱来源难度：普通→普通令，困难→珍稀令，地狱→不朽令。商店箱记录购买时已解锁的所选难度；旧来源不明按普通。</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>待回答</t>
+          <t>用户已批准</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>品质与难度映射一致</t>
+          <t>切换开箱时难度不得改变来源品质</t>
         </is>
       </c>
     </row>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Question pending: extra independent reward versus replacing the original item</t>
+          <t>先判定2%/8%；命中时仅给1令，替代原装备/宝石/材料；未命中才进入原类别池。</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>待回答</t>
+          <t>用户已批准</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>总概率和原奖励口径一致</t>
+          <t>命中不可同时发原奖励，满包失败不耗箱</t>
         </is>
       </c>
     </row>

--- a/docs/design/2026-09-10-hunt-stage-design/GameXXK_讨伐与宝箱设计总表_2026-09-10.xlsx
+++ b/docs/design/2026-09-10-hunt-stage-design/GameXXK_讨伐与宝箱设计总表_2026-09-10.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_讨伐关卡" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_宝箱品质概率" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_门票与奖励规则" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="01_讨伐关卡" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_宝箱品质概率" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_门票与奖励规则" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_九合一品质表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_讨伐关卡'!$A$4:$N$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'01_讨伐关卡'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02_宝箱品质概率'!$A$4:$F$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'02_宝箱品质概率'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02_宝箱品质概率'!$A$4:$G$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03_门票与奖励规则'!$A$4:$D$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'03_门票与奖励规则'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04_九合一品质表'!$A$4:$D$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00&quot;×&quot;"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +58,12 @@
       <name val="Microsoft YaHei"/>
       <color rgb="00243E38"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00183F3A"/>
+      <sz val="18"/>
     </font>
   </fonts>
   <fills count="5">
@@ -94,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,6 +125,13 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -778,34 +792,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>已批准 · 宝箱品质概率</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>装备/宝石分支的条件品质概率；各高品质档精确4倍。先判定门票替代，因此不是每个箱子的无条件出货概率。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>已批准 · 宝箱品质概率（2026-09-11 三箱表 · 基点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="70" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>条件品质概率，单位基点（100 bp = 1%），每列精确合计 10000。珍稀及以上按严格 ×4 阶梯：普通箱 500 → 高级箱 2000 → 讨伐箱 8000（讨伐箱 = 高级箱 ×4 = 普通箱 ×16）。讨伐箱是唯一直出天界/登神/宇宙的来源：天界 80bp、登神 40bp 不分难度，宇宙 16bp 仅地狱；顶端逐级递减（至宝200 &gt; 超凡100 &gt; 天界80 &gt; 登神40 &gt; 宇宙16），无倒挂。普通箱因基点精度止于至宝，高级箱止于超凡。先判定门票（普通箱2%/高级箱8%）替代，故不是每箱的无条件概率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>品质</t>
@@ -813,142 +828,232 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>高级箱概率</t>
+          <t>普通箱</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>讨伐箱概率</t>
+          <t>高级箱</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>概率倍数</t>
+          <t>讨伐箱（普通/困难）</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>讨伐箱（地狱）</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>批准状态</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>实现状态</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>5500</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>用户已批准</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>尚未接入运行时</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>珍稀</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>用户已批准</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>尚未接入运行时</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="B7" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>4800</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>传奇</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>用户已批准</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>尚未接入运行时</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="B8" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>不朽</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>用户已批准</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>尚未接入运行时</t>
-        </is>
+      <c r="B9" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>至宝</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>超凡</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>天界</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>登神</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>宇宙</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F8"/>
+  <autoFilter ref="A4:G14"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1254,4 +1359,185 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>已批准 · 九合一品质规则（2026-09-11 提案B）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="74" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>每次消耗九件同品质同大类（装备或宝石）输入并生成一件结果；失败也消耗全部九件。2026-09-11 提案B：每档只前进一档或保持原品质，**没有跨档跳变**；成功率随档位单一平滑递减 —— 1~3档 100%、4档 90%、5档 85%、6档 80%、7档 75%、8档 70%、9档 60%。期望前进档数 1.00/1.00/1.00/0.90/0.85/0.80/0.75/0.70/0.60，是一条无断点的单调曲线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>输入品质</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>结果分布</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>批准状态</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>实现状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>100% 稀有</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>100% 珍稀</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>珍稀</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>100% 传奇</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>传奇</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>10% 保持传奇 / 90% 不朽</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>不朽</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>15% 保持不朽 / 85% 至宝</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>至宝</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>20% 保持至宝 / 80% 超凡</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>超凡</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>25% 保持超凡 / 75% 天界</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>天界</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>30% 保持天界 / 70% 登神</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>登神</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>40% 保持登神 / 60% 宇宙</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>宇宙</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>品质上限，不允许继续合成</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:D14"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>